--- a/data/trans_bre/P62-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P62-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-43,89; -35,21</t>
+          <t>-43,73; -35,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-28,72; -19,8</t>
+          <t>-29,53; -20,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,0; -20,38</t>
+          <t>-30,2; -20,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,69; -17,05</t>
+          <t>-26,69; -17,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-54,51; -46,2</t>
+          <t>-54,67; -46,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-39,67; -29,48</t>
+          <t>-40,26; -29,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-40,54; -29,36</t>
+          <t>-40,23; -28,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-32,61; -22,58</t>
+          <t>-32,85; -22,73</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-26,27; -17,61</t>
+          <t>-25,45; -17,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,1; -8,48</t>
+          <t>-15,87; -8,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,83; -10,79</t>
+          <t>-18,22; -10,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,73; 19,41</t>
+          <t>-18,88; 17,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-78,33; -64,0</t>
+          <t>-77,75; -63,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,69; -34,79</t>
+          <t>-54,5; -35,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,12; -33,59</t>
+          <t>-50,35; -33,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,03; 50,06</t>
+          <t>-42,14; 43,13</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-30,53; -9,99</t>
+          <t>-30,84; -9,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,53; -1,85</t>
+          <t>-21,43; -2,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,79; -3,98</t>
+          <t>-22,89; -4,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-31,32; -11,95</t>
+          <t>-30,75; -12,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-63,94; -27,52</t>
+          <t>-62,91; -26,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-62,7; -7,33</t>
+          <t>-62,79; -11,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-56,33; -13,68</t>
+          <t>-55,78; -13,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-50,36; -23,75</t>
+          <t>-50,12; -24,51</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,9; -26,51</t>
+          <t>-32,83; -26,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-18,17; -12,13</t>
+          <t>-17,95; -12,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,36; -13,53</t>
+          <t>-19,08; -13,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,61; 4,65</t>
+          <t>-17,7; 5,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,44; -50,7</t>
+          <t>-58,31; -50,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,69; -28,79</t>
+          <t>-39,5; -28,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,07; -29,79</t>
+          <t>-39,91; -29,76</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,11; 8,97</t>
+          <t>-32,35; 10,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P62-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P62-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-21,78</t>
+          <t>-21,14</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-27,82%</t>
+          <t>-27,24%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-43,73; -35,58</t>
+          <t>-44,4; -35,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-29,53; -20,32</t>
+          <t>-28,69; -19,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,2; -20,0</t>
+          <t>-30,8; -20,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-26,69; -17,11</t>
+          <t>-25,86; -16,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-54,67; -46,23</t>
+          <t>-54,83; -46,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-40,26; -29,9</t>
+          <t>-39,88; -29,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-40,23; -28,55</t>
+          <t>-41,07; -28,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-32,85; -22,73</t>
+          <t>-32,27; -22,02</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-5,47</t>
+          <t>-19,44</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-12,58%</t>
+          <t>-43,25%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-25,45; -17,18</t>
+          <t>-25,77; -18,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,87; -8,67</t>
+          <t>-15,79; -8,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-18,22; -10,95</t>
+          <t>-18,04; -10,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 17,99</t>
+          <t>-23,57; -15,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-77,75; -63,71</t>
+          <t>-77,59; -63,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-54,5; -35,19</t>
+          <t>-54,27; -33,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,35; -33,8</t>
+          <t>-50,05; -32,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-42,14; 43,13</t>
+          <t>-49,25; -35,88</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-21,87</t>
+          <t>-22,07</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-39,04%</t>
+          <t>-38,97%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-30,84; -9,55</t>
+          <t>-30,36; -9,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-21,43; -2,54</t>
+          <t>-21,34; -2,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,89; -4,47</t>
+          <t>-22,32; -3,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-30,75; -12,32</t>
+          <t>-29,66; -12,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-62,91; -26,18</t>
+          <t>-62,24; -25,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-62,79; -11,42</t>
+          <t>-62,73; -7,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-55,78; -13,68</t>
+          <t>-55,64; -12,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-50,12; -24,51</t>
+          <t>-48,6; -25,3</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-10,78</t>
+          <t>-18,27</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-19,93%</t>
+          <t>-33,17%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-32,83; -26,46</t>
+          <t>-32,87; -26,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,95; -12,16</t>
+          <t>-17,85; -12,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-19,08; -13,26</t>
+          <t>-19,3; -13,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 5,32</t>
+          <t>-21,59; -14,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-58,31; -50,77</t>
+          <t>-58,51; -50,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,5; -28,78</t>
+          <t>-38,94; -28,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-39,91; -29,76</t>
+          <t>-39,96; -29,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-32,35; 10,14</t>
+          <t>-37,83; -27,75</t>
         </is>
       </c>
     </row>
